--- a/data/03_rail.xlsx
+++ b/data/03_rail.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="R4e9542785b784fa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Operators" sheetId="2" r:id="R71802a82fb234307"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Networks" sheetId="3" r:id="Rf115be9871d24679"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Nodes" sheetId="4" r:id="R3480fc78c1454f8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Links" sheetId="5" r:id="Rccd09eb9e81049d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Relationships" sheetId="6" r:id="Rd8de7cdd67524b78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Fleet" sheetId="7" r:id="R04d12d84d521441c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Connections" sheetId="8" r:id="R5a1f5802a2184460"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail News" sheetId="9" r:id="R22a6c6dc598a4136"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Index" sheetId="1" r:id="Rfcf6f20ac74643e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Operators" sheetId="2" r:id="R0608fc6897dc4297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Networks" sheetId="3" r:id="Ra680a2c17ad642ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Nodes" sheetId="4" r:id="R3633143ac9dd484a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Links" sheetId="5" r:id="R4ae1bc8d98944345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Relationships" sheetId="6" r:id="R107e0d80414a4f71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Fleet" sheetId="7" r:id="R33fef0ea40204e1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail Connections" sheetId="8" r:id="Rcef7521fbe1d49f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rail News" sheetId="9" r:id="R911b276e1c6e4ffd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1249,6 +1249,47 @@
         <x:v>https://dfccil.com/upload/1353697422824.pdf</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" t="str">
+        <x:v>ROP_UA_0001</x:v>
+      </x:c>
+      <x:c r="B21" t="str">
+        <x:v>COMP_UKRZALIZNYTSIA</x:v>
+      </x:c>
+      <x:c r="C21" t="str">
+        <x:v>Ukrzaliznytsia</x:v>
+      </x:c>
+      <x:c r="D21" t="str">
+        <x:v>National railway owner/operator</x:v>
+      </x:c>
+      <x:c r="E21" t="str">
+        <x:v>Ukraine</x:v>
+      </x:c>
+      <x:c r="F21" t="str">
+        <x:v>Freight + passenger + infrastructure</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>National network</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>1520 mm</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>Electrified and diesel network</x:v>
+      </x:c>
+      <x:c r="J21" t="str">
+        <x:v>Operating under wartime conditions</x:v>
+      </x:c>
+      <x:c r="K21" t="str">
+        <x:v>Critical grain, industrial, military and cross-border freight network; recurrent Russian strikes on locomotives, depots and infrastructure.</x:v>
+      </x:c>
+      <x:c r="L21" t="str">
+        <x:v>SRC_SEC_006</x:v>
+      </x:c>
+      <x:c r="M21" t="str">
+        <x:v>https://www.railjournal.com/regions/europe/ukraines-rail-network-comes-under-mounting-russian-attacks/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2176,6 +2217,50 @@
         <x:v>https://www.concorindia.co.in/rail-terminals</x:v>
       </x:c>
     </x:row>
+    <x:row r="22">
+      <x:c r="A22" t="str">
+        <x:v>RAILNET_UA_0001</x:v>
+      </x:c>
+      <x:c r="B22" t="str">
+        <x:v>Ukraine National Rail Freight Network</x:v>
+      </x:c>
+      <x:c r="C22" t="str">
+        <x:v>COMP_UKRZALIZNYTSIA</x:v>
+      </x:c>
+      <x:c r="D22" t="str">
+        <x:v>Ukraine / EU border connections</x:v>
+      </x:c>
+      <x:c r="E22" t="str">
+        <x:v>Black Sea / industrial east / national network</x:v>
+      </x:c>
+      <x:c r="F22" t="str">
+        <x:v>EU border gateways</x:v>
+      </x:c>
+      <x:c r="G22" t="str">
+        <x:v>National network</x:v>
+      </x:c>
+      <x:c r="H22" t="str">
+        <x:v>1520 mm</x:v>
+      </x:c>
+      <x:c r="I22" t="str">
+        <x:v>Mixed electrification</x:v>
+      </x:c>
+      <x:c r="J22" t="str">
+        <x:v>Operating / conflict-degraded</x:v>
+      </x:c>
+      <x:c r="K22" t="str">
+        <x:v>Grain; metals; containers; industrial cargo; humanitarian and defence logistics</x:v>
+      </x:c>
+      <x:c r="L22" t="str">
+        <x:v>Repeated attacks on locomotive depots and critical infrastructure create capacity, maintenance and corridor-reliability risk.</x:v>
+      </x:c>
+      <x:c r="M22" t="str">
+        <x:v>SRC_SEC_006</x:v>
+      </x:c>
+      <x:c r="N22" t="str">
+        <x:v>https://www.railjournal.com/regions/europe/ukraines-rail-network-comes-under-mounting-russian-attacks/</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -7160,6 +7245,64 @@
         <x:v>https://www.norfolksouthern.com/en/ship-by-rail/our-rail-network/intermodal-terminals-schedules</x:v>
       </x:c>
     </x:row>
+    <x:row r="7">
+      <x:c r="A7" t="str">
+        <x:v>RNEWS_SEC_001</x:v>
+      </x:c>
+      <x:c r="B7" t="str">
+        <x:v>2026-09-10</x:v>
+      </x:c>
+      <x:c r="C7" t="str">
+        <x:v>RAILNET_UA_0001</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>COMP_UKRZALIZNYTSIA</x:v>
+      </x:c>
+      <x:c r="E7" t="str">
+        <x:v>Conflict / infrastructure attack</x:v>
+      </x:c>
+      <x:c r="F7" t="str">
+        <x:v>Ukraine rail network comes under mounting Russian attacks</x:v>
+      </x:c>
+      <x:c r="G7" t="str">
+        <x:v>Repeated strikes target locomotives, maintenance depots and critical rail infrastructure, increasing freight-network pressure and repair burden.</x:v>
+      </x:c>
+      <x:c r="H7" t="str">
+        <x:v>SRC_SEC_006</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>https://www.railjournal.com/regions/europe/ukraines-rail-network-comes-under-mounting-russian-attacks/</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" t="str">
+        <x:v>RNEWS_SEC_002</x:v>
+      </x:c>
+      <x:c r="B8" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>RAILNET_UA_0001</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>COMP_UKRZALIZNYTSIA</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>Ballistic missile strike</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>Darnytsia locomotive depot hit</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>Ukrzaliznytsia records a ballistic-missile strike on Darnytsia locomotive depot; a locomotive repair worker later died from injuries.</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>SRC_SEC_007</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>https://zalizna-rodyna.uz.gov.ua/en/memorial/volodimir-gubskiy</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
